--- a/manual/templat-luaran.xlsx
+++ b/manual/templat-luaran.xlsx
@@ -46,6 +46,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 
